--- a/docs/freigabe-katalog/versand-2026-10-25-nachpruefung/steuern/Betriebsklar-Nachpruefliste-Steuerberater.xlsx
+++ b/docs/freigabe-katalog/versand-2026-10-25-nachpruefung/steuern/Betriebsklar-Nachpruefliste-Steuerberater.xlsx
@@ -496,7 +496,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>• Vorlage: Inhalt seit Ihrer Freigabe geändert und/oder ohne unterschriebenes Blatt. Die Prüfsumme bestimmt die Fassung; jede Änderung ergibt eine neue.</t>
+          <t>• Vorlage: ohne unterschriebenes Blatt und/oder eine Variante (Rechtsform, Land, Rechnungsart …) seit Ihrer Freigabe geändert. Je Variante bestimmt eine Prüfsumme die Fassung; eine Änderung betrifft nur ihre Variante.</t>
         </is>
       </c>
     </row>
@@ -520,7 +520,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Am Ende das Blatt „Unterschrift“ ausfüllen und unterschreiben (Scan genügt). Zu den Vorlagen liegen die aktuellen PDFs bei.</t>
+          <t>Am Ende das Blatt „Unterschrift“ ausfüllen und unterschreiben (Scan genügt). Zu geänderten Varianten von Vorlagen liegen PDFs bei (Ordner „vorlagen“).</t>
         </is>
       </c>
     </row>
@@ -535,7 +535,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:H23"/>
+  <dimension ref="A1:H19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -862,7 +862,7 @@
       </c>
       <c r="D10" s="3" t="inlineStr">
         <is>
-          <t>cd5d8fd718c1</t>
+          <t>b1bf4530cee8</t>
         </is>
       </c>
       <c r="E10" s="3" t="inlineStr">
@@ -872,7 +872,7 @@
       </c>
       <c r="F10" s="3" t="inlineStr">
         <is>
-          <t>Seit Ihrer Freigabe geändert: die Fußzeile bei GmbH &amp; Co. KG und UG (haftungsbeschränkt) &amp; Co. KG (Zeile „Persönlich haftende Gesellschafterin: …“ mit den Angaben der Komplementärin, E-193) sowie das Storno einer Schlussrechnung (die abgesetzten Abschlagsrechnungen werden mit umgekehrtem Vorzeichen gespiegelt, E-193). Prüfsumme der freigegebenen Fassung 291e2da869c3 (bisherige Rechnung 8c2e773d4153), heute cd5d8fd718c1. Bitte die heutige Fassung (Prüfsumme rechts) durchsehen und bestätigen.</t>
+          <t>Seit Ihrer Freigabe geändert sind nur diese Varianten: GmbH &amp; Co. KG; UG (haftungsbeschränkt) &amp; Co. KG; Storno einer Schlussrechnung mit Abschlägen (die abgesetzten Abschlagsrechnungen werden mit umgekehrtem Vorzeichen gespiegelt, E-193) – bei GmbH &amp; Co. KG / UG &amp; Co. KG die Fußzeile mit der Zeile „Persönlich haftende Gesellschafterin: …“ (Angaben der Komplementärin, E-193). Die übrigen 30 von 33 Varianten (Rechtsformen, Länder, Kleinunternehmer, Schlussrechnung, Storno) sind unverändert; für sie gilt Ihre Freigabe weiter. Beispiel-PDFs der geänderten Varianten: vorlagen/rechnung-gmbh-co-kg.pdf, vorlagen/rechnung-ug-co-kg.pdf, vorlagen/rechnung-storno-schlussrechnung.pdf. Bitte die geänderten Varianten durchsehen und bestätigen.</t>
         </is>
       </c>
       <c r="G10" s="3" t="inlineStr"/>
@@ -889,22 +889,22 @@
       </c>
       <c r="C11" s="3" t="inlineStr">
         <is>
-          <t>euer</t>
+          <t>ust_voranmeldung</t>
         </is>
       </c>
       <c r="D11" s="3" t="inlineStr">
         <is>
-          <t>bb9ed4e7520c</t>
+          <t>c0939d610d67</t>
         </is>
       </c>
       <c r="E11" s="3" t="inlineStr">
         <is>
-          <t>Einnahmen-Überschuss-Rechnung (EÜR)</t>
+          <t>Umsatzsteuer-Voranmeldung</t>
         </is>
       </c>
       <c r="F11" s="3" t="inlineStr">
         <is>
-          <t>Seit Ihrer Freigabe geändert: die Fußzeile bei GmbH &amp; Co. KG und UG (haftungsbeschränkt) &amp; Co. KG (Zeile „Persönlich haftende Gesellschafterin: …“ mit den Angaben der Komplementärin, E-193). Prüfsumme der freigegebenen Fassung 11961141abd0 (bisherige Rechnung d669212fbf4a), heute bb9ed4e7520c. Bitte die heutige Fassung (Prüfsumme rechts) durchsehen und bestätigen.</t>
+          <t>Ein unterschriebenes Blatt liegt uns nicht vor (Die Ergänzung der Bestätigung trägt keine Unterschrift). Inhalt seit Ihrer Freigabe unverändert – bitte nur die Freigabe mit Unterschrift bestätigen.</t>
         </is>
       </c>
       <c r="G11" s="3" t="inlineStr"/>
@@ -921,22 +921,22 @@
       </c>
       <c r="C12" s="3" t="inlineStr">
         <is>
-          <t>verfahrensdokumentation</t>
+          <t>oss_meldung</t>
         </is>
       </c>
       <c r="D12" s="3" t="inlineStr">
         <is>
-          <t>ac4871272df6</t>
+          <t>4416d2cf8a9c</t>
         </is>
       </c>
       <c r="E12" s="3" t="inlineStr">
         <is>
-          <t>Verfahrensdokumentation (GoBD)</t>
+          <t>OSS-Erklärung (One-Stop-Shop)</t>
         </is>
       </c>
       <c r="F12" s="3" t="inlineStr">
         <is>
-          <t>Seit Ihrer Freigabe geändert: die Fußzeile bei GmbH &amp; Co. KG und UG (haftungsbeschränkt) &amp; Co. KG (Zeile „Persönlich haftende Gesellschafterin: …“ mit den Angaben der Komplementärin, E-193). Prüfsumme der freigegebenen Fassung 900addfd4c97 (bisherige Rechnung 9d23a5d3f018), heute ac4871272df6. Bitte die heutige Fassung (Prüfsumme rechts) durchsehen und bestätigen.</t>
+          <t>Ein unterschriebenes Blatt liegt uns nicht vor (Die Ergänzung der Bestätigung trägt keine Unterschrift). Inhalt seit Ihrer Freigabe unverändert – bitte nur die Freigabe mit Unterschrift bestätigen.</t>
         </is>
       </c>
       <c r="G12" s="3" t="inlineStr"/>
@@ -953,22 +953,22 @@
       </c>
       <c r="C13" s="3" t="inlineStr">
         <is>
-          <t>kassenmeldung</t>
+          <t>zm_meldung</t>
         </is>
       </c>
       <c r="D13" s="3" t="inlineStr">
         <is>
-          <t>37630d0e2ef3</t>
+          <t>332a518a08d5</t>
         </is>
       </c>
       <c r="E13" s="3" t="inlineStr">
         <is>
-          <t>Kassenmeldung (Datenblatt)</t>
+          <t>Zusammenfassende Meldung</t>
         </is>
       </c>
       <c r="F13" s="3" t="inlineStr">
         <is>
-          <t>Seit Ihrer Freigabe geändert: die Fußzeile bei GmbH &amp; Co. KG und UG (haftungsbeschränkt) &amp; Co. KG (Zeile „Persönlich haftende Gesellschafterin: …“ mit den Angaben der Komplementärin, E-193). Prüfsumme der freigegebenen Fassung 7dc7ad6cb636 (bisherige Rechnung d9ac127520ba), heute 37630d0e2ef3. Bitte die heutige Fassung (Prüfsumme rechts) durchsehen und bestätigen.</t>
+          <t>Ein unterschriebenes Blatt liegt uns nicht vor (Die Ergänzung der Bestätigung trägt keine Unterschrift). Inhalt seit Ihrer Freigabe unverändert – bitte nur die Freigabe mit Unterschrift bestätigen.</t>
         </is>
       </c>
       <c r="G13" s="3" t="inlineStr"/>
@@ -985,22 +985,22 @@
       </c>
       <c r="C14" s="3" t="inlineStr">
         <is>
-          <t>lohnkonto</t>
+          <t>steuererklaerung</t>
         </is>
       </c>
       <c r="D14" s="3" t="inlineStr">
         <is>
-          <t>25d655ce74ee</t>
+          <t>c5f459479a06</t>
         </is>
       </c>
       <c r="E14" s="3" t="inlineStr">
         <is>
-          <t>Lohnkonto-Übersicht (aus den Abrechnungen)</t>
+          <t>Unterlagen zur Steuererklärung</t>
         </is>
       </c>
       <c r="F14" s="3" t="inlineStr">
         <is>
-          <t>Seit Ihrer Freigabe geändert: die Fußzeile bei GmbH &amp; Co. KG und UG (haftungsbeschränkt) &amp; Co. KG (Zeile „Persönlich haftende Gesellschafterin: …“ mit den Angaben der Komplementärin, E-193). Prüfsumme der freigegebenen Fassung c3c944218075 (bisherige Rechnung 7210085d37a2), heute 25d655ce74ee. Bitte die heutige Fassung (Prüfsumme rechts) durchsehen und bestätigen.</t>
+          <t>Ein unterschriebenes Blatt liegt uns nicht vor (Die Ergänzung der Bestätigung trägt keine Unterschrift). Inhalt seit Ihrer Freigabe unverändert – bitte nur die Freigabe mit Unterschrift bestätigen.</t>
         </is>
       </c>
       <c r="G14" s="3" t="inlineStr"/>
@@ -1017,22 +1017,22 @@
       </c>
       <c r="C15" s="3" t="inlineStr">
         <is>
-          <t>ust_voranmeldung</t>
+          <t>kassenbuch</t>
         </is>
       </c>
       <c r="D15" s="3" t="inlineStr">
         <is>
-          <t>0727eb11025b</t>
+          <t>9cad79a55cbc</t>
         </is>
       </c>
       <c r="E15" s="3" t="inlineStr">
         <is>
-          <t>Umsatzsteuer-Voranmeldung</t>
+          <t>Kassenbuch</t>
         </is>
       </c>
       <c r="F15" s="3" t="inlineStr">
         <is>
-          <t>Seit Ihrer Freigabe geändert: die Fußzeile bei GmbH &amp; Co. KG und UG (haftungsbeschränkt) &amp; Co. KG (Zeile „Persönlich haftende Gesellschafterin: …“ mit den Angaben der Komplementärin, E-193). Prüfsumme der freigegebenen Fassung 1658a19a8433 (bisherige Rechnung fa59f364368d), heute 0727eb11025b. Ein unterschriebenes Blatt liegt uns nicht vor (Die Ergänzung der Bestätigung trägt keine Unterschrift). Bitte die heutige Fassung (Prüfsumme rechts) durchsehen und bestätigen.</t>
+          <t>Ein unterschriebenes Blatt liegt uns nicht vor (Die Ergänzung der Bestätigung trägt keine Unterschrift). Inhalt seit Ihrer Freigabe unverändert – bitte nur die Freigabe mit Unterschrift bestätigen.</t>
         </is>
       </c>
       <c r="G15" s="3" t="inlineStr"/>
@@ -1049,22 +1049,22 @@
       </c>
       <c r="C16" s="3" t="inlineStr">
         <is>
-          <t>oss_meldung</t>
+          <t>aufbewahrung</t>
         </is>
       </c>
       <c r="D16" s="3" t="inlineStr">
         <is>
-          <t>a7c4beec0949</t>
+          <t>0ebd0adde12a</t>
         </is>
       </c>
       <c r="E16" s="3" t="inlineStr">
         <is>
-          <t>OSS-Erklärung (One-Stop-Shop)</t>
+          <t>Aufbewahrungsplan</t>
         </is>
       </c>
       <c r="F16" s="3" t="inlineStr">
         <is>
-          <t>Seit Ihrer Freigabe geändert: die Fußzeile bei GmbH &amp; Co. KG und UG (haftungsbeschränkt) &amp; Co. KG (Zeile „Persönlich haftende Gesellschafterin: …“ mit den Angaben der Komplementärin, E-193). Prüfsumme der freigegebenen Fassung a2b746134812 (bisherige Rechnung f136b58ddfcc), heute a7c4beec0949. Ein unterschriebenes Blatt liegt uns nicht vor (Die Ergänzung der Bestätigung trägt keine Unterschrift). Bitte die heutige Fassung (Prüfsumme rechts) durchsehen und bestätigen.</t>
+          <t>Ein unterschriebenes Blatt liegt uns nicht vor (Die Ergänzung der Bestätigung trägt keine Unterschrift). Inhalt seit Ihrer Freigabe unverändert – bitte nur die Freigabe mit Unterschrift bestätigen.</t>
         </is>
       </c>
       <c r="G16" s="3" t="inlineStr"/>
@@ -1081,22 +1081,22 @@
       </c>
       <c r="C17" s="3" t="inlineStr">
         <is>
-          <t>zm_meldung</t>
+          <t>sv_meldedaten</t>
         </is>
       </c>
       <c r="D17" s="3" t="inlineStr">
         <is>
-          <t>dcaf6715770f</t>
+          <t>6823730ddb14</t>
         </is>
       </c>
       <c r="E17" s="3" t="inlineStr">
         <is>
-          <t>Zusammenfassende Meldung</t>
+          <t>Personalfragebogen (Daten für die Anmeldung)</t>
         </is>
       </c>
       <c r="F17" s="3" t="inlineStr">
         <is>
-          <t>Seit Ihrer Freigabe geändert: die Fußzeile bei GmbH &amp; Co. KG und UG (haftungsbeschränkt) &amp; Co. KG (Zeile „Persönlich haftende Gesellschafterin: …“ mit den Angaben der Komplementärin, E-193). Prüfsumme der freigegebenen Fassung 5dc5e94a8ec8 (bisherige Rechnung f7a989efdb3e), heute dcaf6715770f. Ein unterschriebenes Blatt liegt uns nicht vor (Die Ergänzung der Bestätigung trägt keine Unterschrift). Bitte die heutige Fassung (Prüfsumme rechts) durchsehen und bestätigen.</t>
+          <t>Ein unterschriebenes Blatt liegt uns nicht vor (Die Ergänzung der Bestätigung trägt keine Unterschrift). Inhalt seit Ihrer Freigabe unverändert – bitte nur die Freigabe mit Unterschrift bestätigen.</t>
         </is>
       </c>
       <c r="G17" s="3" t="inlineStr"/>
@@ -1113,22 +1113,22 @@
       </c>
       <c r="C18" s="3" t="inlineStr">
         <is>
-          <t>steuererklaerung</t>
+          <t>bilanz_guv</t>
         </is>
       </c>
       <c r="D18" s="3" t="inlineStr">
         <is>
-          <t>ac9179b53a06</t>
+          <t>a266993aadfd</t>
         </is>
       </c>
       <c r="E18" s="3" t="inlineStr">
         <is>
-          <t>Unterlagen zur Steuererklärung</t>
+          <t>Bilanz und Gewinn- und Verlustrechnung</t>
         </is>
       </c>
       <c r="F18" s="3" t="inlineStr">
         <is>
-          <t>Seit Ihrer Freigabe geändert: die Fußzeile bei GmbH &amp; Co. KG und UG (haftungsbeschränkt) &amp; Co. KG (Zeile „Persönlich haftende Gesellschafterin: …“ mit den Angaben der Komplementärin, E-193). Prüfsumme der freigegebenen Fassung 5a34a0072e9b (bisherige Rechnung 77c6acbdf298), heute ac9179b53a06. Ein unterschriebenes Blatt liegt uns nicht vor (Die Ergänzung der Bestätigung trägt keine Unterschrift). Bitte die heutige Fassung (Prüfsumme rechts) durchsehen und bestätigen.</t>
+          <t>Seit Ihrer Freigabe geändert sind nur diese Varianten: Hilfetext eines Formularfelds: „Steuerberater“ statt Ihres Namens (das gedruckte Dokument ist unverändert). Die übrigen 29 von 30 Varianten (Rechtsformen, Länder, Kleinunternehmer) sind unverändert; für sie gilt Ihre Freigabe weiter. Ein unterschriebenes Blatt liegt uns nicht vor (Die Mail vom 25.10.2026 nennt den Nachtrag „unterschrieben“; die angehängte Datei (und 2026-10-25-nachtrag-bilanz-steuern.pdf) trägt keine Unterschrift). Bitte die geänderten Varianten durchsehen und bestätigen.</t>
         </is>
       </c>
       <c r="G18" s="3" t="inlineStr"/>
@@ -1140,163 +1140,35 @@
       </c>
       <c r="B19" s="3" t="inlineStr">
         <is>
-          <t>Vorlage</t>
+          <t>Nennung im Vermerk</t>
         </is>
       </c>
       <c r="C19" s="3" t="inlineStr">
         <is>
-          <t>kassenbuch</t>
+          <t>alle</t>
         </is>
       </c>
       <c r="D19" s="3" t="inlineStr">
         <is>
-          <t>d301fb300d3c</t>
+          <t>–</t>
         </is>
       </c>
       <c r="E19" s="3" t="inlineStr">
         <is>
-          <t>Kassenbuch</t>
+          <t>Rolle statt Name</t>
         </is>
       </c>
       <c r="F19" s="3" t="inlineStr">
         <is>
-          <t>Seit Ihrer Freigabe geändert: die Fußzeile bei GmbH &amp; Co. KG und UG (haftungsbeschränkt) &amp; Co. KG (Zeile „Persönlich haftende Gesellschafterin: …“ mit den Angaben der Komplementärin, E-193). Prüfsumme der freigegebenen Fassung ac5bf1039bb2 (bisherige Rechnung cda4e6656204), heute d301fb300d3c. Ein unterschriebenes Blatt liegt uns nicht vor (Die Ergänzung der Bestätigung trägt keine Unterschrift). Bitte die heutige Fassung (Prüfsumme rechts) durchsehen und bestätigen.</t>
+          <t>Die App nennt Personen nicht mehr. Bisher mit Ihrem Namen und der Kanzlei (Ihre Bestätigung vom 23.10.2026); künftig nennt der Vermerk Ihre Rolle: „Fachlich durchgesehen von einem Steuerberater (Stand …) – ohne Gewähr für den Einzelfall.“ (bei Einschränkungen mit dem Zusatz in Klammern, bei offenen Punkten „teilweise“). Bitte bestätigen, dass die Nennung der Rolle so in Ordnung ist.</t>
         </is>
       </c>
       <c r="G19" s="3" t="inlineStr"/>
       <c r="H19" s="3" t="inlineStr"/>
     </row>
-    <row r="20">
-      <c r="A20" s="3" t="n">
-        <v>19</v>
-      </c>
-      <c r="B20" s="3" t="inlineStr">
-        <is>
-          <t>Vorlage</t>
-        </is>
-      </c>
-      <c r="C20" s="3" t="inlineStr">
-        <is>
-          <t>aufbewahrung</t>
-        </is>
-      </c>
-      <c r="D20" s="3" t="inlineStr">
-        <is>
-          <t>4f6817b30fa9</t>
-        </is>
-      </c>
-      <c r="E20" s="3" t="inlineStr">
-        <is>
-          <t>Aufbewahrungsplan</t>
-        </is>
-      </c>
-      <c r="F20" s="3" t="inlineStr">
-        <is>
-          <t>Seit Ihrer Freigabe geändert: die Fußzeile bei GmbH &amp; Co. KG und UG (haftungsbeschränkt) &amp; Co. KG (Zeile „Persönlich haftende Gesellschafterin: …“ mit den Angaben der Komplementärin, E-193). Prüfsumme der freigegebenen Fassung 1b052ee4df0d (bisherige Rechnung 0582763257c6), heute 4f6817b30fa9. Ein unterschriebenes Blatt liegt uns nicht vor (Die Ergänzung der Bestätigung trägt keine Unterschrift). Bitte die heutige Fassung (Prüfsumme rechts) durchsehen und bestätigen.</t>
-        </is>
-      </c>
-      <c r="G20" s="3" t="inlineStr"/>
-      <c r="H20" s="3" t="inlineStr"/>
-    </row>
-    <row r="21">
-      <c r="A21" s="3" t="n">
-        <v>20</v>
-      </c>
-      <c r="B21" s="3" t="inlineStr">
-        <is>
-          <t>Vorlage</t>
-        </is>
-      </c>
-      <c r="C21" s="3" t="inlineStr">
-        <is>
-          <t>sv_meldedaten</t>
-        </is>
-      </c>
-      <c r="D21" s="3" t="inlineStr">
-        <is>
-          <t>7ba032d17786</t>
-        </is>
-      </c>
-      <c r="E21" s="3" t="inlineStr">
-        <is>
-          <t>Personalfragebogen (Daten für die Anmeldung)</t>
-        </is>
-      </c>
-      <c r="F21" s="3" t="inlineStr">
-        <is>
-          <t>Seit Ihrer Freigabe geändert: die Fußzeile bei GmbH &amp; Co. KG und UG (haftungsbeschränkt) &amp; Co. KG (Zeile „Persönlich haftende Gesellschafterin: …“ mit den Angaben der Komplementärin, E-193). Prüfsumme der freigegebenen Fassung f60539f8f7c1 (bisherige Rechnung 71ff4c2ff820), heute 7ba032d17786. Ein unterschriebenes Blatt liegt uns nicht vor (Die Ergänzung der Bestätigung trägt keine Unterschrift). Bitte die heutige Fassung (Prüfsumme rechts) durchsehen und bestätigen.</t>
-        </is>
-      </c>
-      <c r="G21" s="3" t="inlineStr"/>
-      <c r="H21" s="3" t="inlineStr"/>
-    </row>
-    <row r="22">
-      <c r="A22" s="3" t="n">
-        <v>21</v>
-      </c>
-      <c r="B22" s="3" t="inlineStr">
-        <is>
-          <t>Vorlage</t>
-        </is>
-      </c>
-      <c r="C22" s="3" t="inlineStr">
-        <is>
-          <t>bilanz_guv</t>
-        </is>
-      </c>
-      <c r="D22" s="3" t="inlineStr">
-        <is>
-          <t>3825054480fd</t>
-        </is>
-      </c>
-      <c r="E22" s="3" t="inlineStr">
-        <is>
-          <t>Bilanz und Gewinn- und Verlustrechnung</t>
-        </is>
-      </c>
-      <c r="F22" s="3" t="inlineStr">
-        <is>
-          <t>Seit Ihrer Freigabe geändert: die Fußzeile bei GmbH &amp; Co. KG und UG (haftungsbeschränkt) &amp; Co. KG (Zeile „Persönlich haftende Gesellschafterin: …“ mit den Angaben der Komplementärin, E-193). Prüfsumme der freigegebenen Fassung b981291ce70e (bisherige Rechnung 5d2246459fe6), heute 3825054480fd. Ein unterschriebenes Blatt liegt uns nicht vor (Die Mail vom 25.10.2026 nennt den Nachtrag „unterschrieben“; die angehängte Datei (und 2026-10-25-nachtrag-bilanz-steuern.pdf) trägt keine Unterschrift). Bitte die heutige Fassung (Prüfsumme rechts) durchsehen und bestätigen.</t>
-        </is>
-      </c>
-      <c r="G22" s="3" t="inlineStr"/>
-      <c r="H22" s="3" t="inlineStr"/>
-    </row>
-    <row r="23">
-      <c r="A23" s="3" t="n">
-        <v>22</v>
-      </c>
-      <c r="B23" s="3" t="inlineStr">
-        <is>
-          <t>Nennung im Vermerk</t>
-        </is>
-      </c>
-      <c r="C23" s="3" t="inlineStr">
-        <is>
-          <t>alle</t>
-        </is>
-      </c>
-      <c r="D23" s="3" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
-      </c>
-      <c r="E23" s="3" t="inlineStr">
-        <is>
-          <t>Rolle statt Name</t>
-        </is>
-      </c>
-      <c r="F23" s="3" t="inlineStr">
-        <is>
-          <t>Die App nennt Personen nicht mehr. Bisher mit Ihrem Namen und der Kanzlei (Ihre Bestätigung vom 23.10.2026); künftig nennt der Vermerk Ihre Rolle: „Fachlich durchgesehen von einem Steuerberater (Stand …) – ohne Gewähr für den Einzelfall.“ (bei Einschränkungen mit dem Zusatz in Klammern, bei offenen Punkten „teilweise“). Bitte bestätigen, dass die Nennung der Rolle so in Ordnung ist.</t>
-        </is>
-      </c>
-      <c r="G23" s="3" t="inlineStr"/>
-      <c r="H23" s="3" t="inlineStr"/>
-    </row>
   </sheetData>
   <dataValidations count="1">
-    <dataValidation sqref="G2:G23" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="G2:G19" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"bestätigt,ändern (Anmerkung),nicht mein Bereich"</formula1>
     </dataValidation>
   </dataValidations>

--- a/docs/freigabe-katalog/versand-2026-10-25-nachpruefung/steuern/Betriebsklar-Nachpruefliste-Steuerberater.xlsx
+++ b/docs/freigabe-katalog/versand-2026-10-25-nachpruefung/steuern/Betriebsklar-Nachpruefliste-Steuerberater.xlsx
@@ -9,7 +9,6 @@
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="So geht's" sheetId="1" state="visible" r:id="rId1"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Nachprüfliste" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Unterschrift" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -19,7 +18,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="4">
+  <fonts count="3">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -34,9 +33,6 @@
     <font>
       <b val="1"/>
       <color rgb="00FFFFFF"/>
-    </font>
-    <font>
-      <b val="1"/>
     </font>
   </fonts>
   <fills count="3">
@@ -78,7 +74,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -87,10 +83,6 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -475,14 +467,14 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Bitte prüfen und bestätigen. Diese Liste nennt alles, was nach unserer Durchsicht der Freigaben noch Ihre Prüfung oder Ihre Unterschrift braucht:</t>
+          <t>Bitte prüfen Sie die Positionen und bestätigen Sie sie per E-Mail. Diese Liste nennt alles, was nach unserer Durchsicht der Freigaben noch Ihre Prüfung oder Bestätigung braucht:</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>• Unterschrift fehlt: Sie haben die Fassung freigegeben, uns liegt aber kein unterschriebenes Blatt vor. Bis dahin zeigt die App bei diesen Einträgen keinen Prüfvermerk.</t>
+          <t>• Bestätigung fehlt: Sie haben die Fassung freigegeben, uns liegt aber keine schriftliche Bestätigung vor. Bis dahin zeigt die App bei diesen Einträgen keinen Prüfvermerk.</t>
         </is>
       </c>
     </row>
@@ -496,7 +488,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>• Vorlage: ohne unterschriebenes Blatt und/oder eine Variante (Rechtsform, Land, Rechnungsart …) seit Ihrer Freigabe geändert. Je Variante bestimmt eine Prüfsumme die Fassung; eine Änderung betrifft nur ihre Variante.</t>
+          <t>• Vorlage: ohne schriftliche Bestätigung und/oder eine Variante (Rechtsform, Land, Rechnungsart …) seit Ihrer Freigabe geändert. Je Variante bestimmt eine Prüfsumme die Fassung; eine Änderung betrifft nur ihre Variante.</t>
         </is>
       </c>
     </row>
@@ -520,7 +512,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Am Ende das Blatt „Unterschrift“ ausfüllen und unterschreiben (Scan genügt). Zu geänderten Varianten von Vorlagen liegen PDFs bei (Ordner „vorlagen“).</t>
+          <t>Bestätigen Sie bitte per E-Mail – eine Unterschrift ist nicht nötig. Es genügt eine kurze Antwort mit den Nummern der bestätigten Positionen, oder Sie schicken diese Datei mit ausgefüllter Spalte „Entscheidung“ mit Ihrer Antwort zurück. Zu geänderten Varianten von Vorlagen liegen PDFs bei (Ordner „vorlagen“).</t>
         </is>
       </c>
     </row>
@@ -535,7 +527,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:H19"/>
+  <dimension ref="A1:H6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -596,27 +588,27 @@
       </c>
       <c r="B2" s="3" t="inlineStr">
         <is>
-          <t>Unterschrift fehlt</t>
+          <t>Offener Punkt</t>
         </is>
       </c>
       <c r="C2" s="3" t="inlineStr">
         <is>
-          <t>B.18 gesellschaft.jahresabschluss_personenhandel</t>
+          <t>C.30 steuern.e_rechnung_versand_2027</t>
         </is>
       </c>
       <c r="D2" s="3" t="inlineStr">
         <is>
-          <t>v2</t>
+          <t>v3</t>
         </is>
       </c>
       <c r="E2" s="3" t="inlineStr">
         <is>
-          <t>Jahresabschluss aufstellen (OHG, KG, e. K.)</t>
+          <t>E-Rechnungen versenden (ab 2027)</t>
         </is>
       </c>
       <c r="F2" s="3" t="inlineStr">
         <is>
-          <t>Sie haben diese Fassung freigegeben (alle Felder; 2026-10-25-runde4-katalog-steuern.xlsx, Stand 25.10.2026). Ein unterschriebenes Blatt liegt uns nicht vor (Mail 25.10.2026 (2026-10-25-steuern-bilanz-mail.txt) nennt den unterschriebenen Nachtrag als Anlage; er liegt uns nicht vor). Bitte die Freigabe dieser Fassung mit Unterschrift bestätigen.</t>
+          <t>In unseren Prüfnotizen offen: Übergangsfristen vor dem Start erneut zu prüfen. Bis zur Klärung zeigt die App „teilweise geprüft – noch offen: Übergangsfristen vor dem Start erneut zu prüfen“. Bitte prüfen Sie den Punkt und bestätigen Sie ihn per E-Mail bzw. nennen Sie die Änderung.</t>
         </is>
       </c>
       <c r="G2" s="3" t="inlineStr"/>
@@ -628,27 +620,27 @@
       </c>
       <c r="B3" s="3" t="inlineStr">
         <is>
-          <t>Unterschrift fehlt</t>
+          <t>Offener Punkt</t>
         </is>
       </c>
       <c r="C3" s="3" t="inlineStr">
         <is>
-          <t>C.28 steuern.buchfuehrungspflicht</t>
+          <t>C.30 steuern.e_rechnung_versand_2028</t>
         </is>
       </c>
       <c r="D3" s="3" t="inlineStr">
         <is>
-          <t>v7</t>
+          <t>v3</t>
         </is>
       </c>
       <c r="E3" s="3" t="inlineStr">
         <is>
-          <t>Doppelte Buchführung</t>
+          <t>E-Rechnungen versenden (ab 2028)</t>
         </is>
       </c>
       <c r="F3" s="3" t="inlineStr">
         <is>
-          <t>Sie haben diese Fassung freigegeben (alle Felder; 2026-10-23-nachpruefung-vorlagen-steuern-mail.txt, Stand 23.10.2026). Ein unterschriebenes Blatt liegt uns nicht vor (Freigabe per Mail 23.10.2026; die Ergänzung der Bestätigung (2026-10-24-ergaenzung-bestaetigung-steuern.pdf) trägt keine Unterschrift). Bitte die Freigabe dieser Fassung mit Unterschrift bestätigen.</t>
+          <t>In unseren Prüfnotizen offen: Übergangsfristen vor dem Start erneut zu prüfen. Bis zur Klärung zeigt die App „teilweise geprüft – noch offen: Übergangsfristen vor dem Start erneut zu prüfen“. Bitte prüfen Sie den Punkt und bestätigen Sie ihn per E-Mail bzw. nennen Sie die Änderung.</t>
         </is>
       </c>
       <c r="G3" s="3" t="inlineStr"/>
@@ -660,27 +652,27 @@
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>Unterschrift fehlt</t>
+          <t>Vorlage</t>
         </is>
       </c>
       <c r="C4" s="3" t="inlineStr">
         <is>
-          <t>B.18 steuern.e_bilanz</t>
+          <t>rechnung</t>
         </is>
       </c>
       <c r="D4" s="3" t="inlineStr">
         <is>
-          <t>v6</t>
+          <t>b1bf4530cee8</t>
         </is>
       </c>
       <c r="E4" s="3" t="inlineStr">
         <is>
-          <t>E-Bilanz ans Finanzamt übermitteln</t>
+          <t>Rechnung</t>
         </is>
       </c>
       <c r="F4" s="3" t="inlineStr">
         <is>
-          <t>Sie haben diese Fassung freigegeben (alle Felder; 2026-10-23-nachpruefung-vorlagen-steuern-mail.txt, Stand 23.10.2026). Ein unterschriebenes Blatt liegt uns nicht vor (Freigabe per Mail 23.10.2026; die Ergänzung der Bestätigung (2026-10-24-ergaenzung-bestaetigung-steuern.pdf) trägt keine Unterschrift). Bitte die Freigabe dieser Fassung mit Unterschrift bestätigen.</t>
+          <t>Seit Ihrer Freigabe geändert sind nur diese Varianten: GmbH &amp; Co. KG; UG (haftungsbeschränkt) &amp; Co. KG; Storno einer Schlussrechnung mit Abschlägen (die abgesetzten Abschlagsrechnungen werden mit umgekehrtem Vorzeichen gespiegelt, E-193) – bei GmbH &amp; Co. KG / UG &amp; Co. KG die Fußzeile mit der Zeile „Persönlich haftende Gesellschafterin: …“ (Angaben der Komplementärin, E-193). Die übrigen 30 von 33 Varianten (Rechtsformen, Länder, Kleinunternehmer, Schlussrechnung, Storno) sind unverändert; für sie gilt Ihre Freigabe weiter, die App zeigt dort den Vermerk. Beispiel-PDFs der geänderten Varianten: vorlagen/rechnung-gmbh-co-kg.pdf, vorlagen/rechnung-ug-co-kg.pdf, vorlagen/rechnung-storno-schlussrechnung.pdf. Bitte sehen Sie die geänderten Varianten durch und bestätigen Sie sie per E-Mail.</t>
         </is>
       </c>
       <c r="G4" s="3" t="inlineStr"/>
@@ -692,27 +684,27 @@
       </c>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>Offener Punkt</t>
+          <t>Vorlage</t>
         </is>
       </c>
       <c r="C5" s="3" t="inlineStr">
         <is>
-          <t>C.30 steuern.e_rechnung_versand_2027</t>
+          <t>bilanz_guv</t>
         </is>
       </c>
       <c r="D5" s="3" t="inlineStr">
         <is>
-          <t>v3</t>
+          <t>a266993aadfd</t>
         </is>
       </c>
       <c r="E5" s="3" t="inlineStr">
         <is>
-          <t>E-Rechnungen versenden (ab 2027)</t>
+          <t>Bilanz und Gewinn- und Verlustrechnung</t>
         </is>
       </c>
       <c r="F5" s="3" t="inlineStr">
         <is>
-          <t>In unseren Prüfnotizen offen: Übergangsfristen vor dem Start erneut zu prüfen. Bis zur Klärung zeigt die App „teilweise geprüft – noch offen: Übergangsfristen vor dem Start erneut zu prüfen“. Bitte prüfen und bestätigen bzw. die Änderung angeben.</t>
+          <t>Seit Ihrer Freigabe geändert sind nur diese Varianten: Hilfetext eines Formularfelds: „Steuerberater“ statt Ihres Namens (das gedruckte Dokument ist unverändert). Die übrigen 29 von 30 Varianten (Rechtsformen, Länder, Kleinunternehmer) sind unverändert; für sie gilt Ihre Freigabe weiter, die App zeigt dort den Vermerk. Bitte sehen Sie die geänderten Varianten durch und bestätigen Sie sie per E-Mail.</t>
         </is>
       </c>
       <c r="G5" s="3" t="inlineStr"/>
@@ -724,547 +716,39 @@
       </c>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>Offener Punkt</t>
+          <t>Nennung im Vermerk</t>
         </is>
       </c>
       <c r="C6" s="3" t="inlineStr">
         <is>
-          <t>C.30 steuern.e_rechnung_versand_2028</t>
+          <t>alle</t>
         </is>
       </c>
       <c r="D6" s="3" t="inlineStr">
         <is>
-          <t>v3</t>
+          <t>–</t>
         </is>
       </c>
       <c r="E6" s="3" t="inlineStr">
         <is>
-          <t>E-Rechnungen versenden (ab 2028)</t>
+          <t>Rolle statt Name</t>
         </is>
       </c>
       <c r="F6" s="3" t="inlineStr">
         <is>
-          <t>In unseren Prüfnotizen offen: Übergangsfristen vor dem Start erneut zu prüfen. Bis zur Klärung zeigt die App „teilweise geprüft – noch offen: Übergangsfristen vor dem Start erneut zu prüfen“. Bitte prüfen und bestätigen bzw. die Änderung angeben.</t>
+          <t>Die App nennt Personen nicht mehr. Bisher mit Ihrem Namen und der Kanzlei (Ihre Bestätigung vom 23.10.2026); künftig nennt der Vermerk Ihre Rolle: „Fachlich durchgesehen von einem Steuerberater (Stand …) – ohne Gewähr für den Einzelfall.“ (bei Einschränkungen mit dem Zusatz in Klammern, bei offenen Punkten „teilweise“). Bitte bestätigen Sie per E-Mail, dass die Nennung der Rolle so in Ordnung ist.</t>
         </is>
       </c>
       <c r="G6" s="3" t="inlineStr"/>
       <c r="H6" s="3" t="inlineStr"/>
     </row>
-    <row r="7">
-      <c r="A7" s="3" t="n">
-        <v>6</v>
-      </c>
-      <c r="B7" s="3" t="inlineStr">
-        <is>
-          <t>Unterschrift fehlt</t>
-        </is>
-      </c>
-      <c r="C7" s="3" t="inlineStr">
-        <is>
-          <t>C.27 steuern.euer</t>
-        </is>
-      </c>
-      <c r="D7" s="3" t="inlineStr">
-        <is>
-          <t>v6</t>
-        </is>
-      </c>
-      <c r="E7" s="3" t="inlineStr">
-        <is>
-          <t>Einnahmen-Überschuss-Rechnung (Anlage EÜR) abgeben</t>
-        </is>
-      </c>
-      <c r="F7" s="3" t="inlineStr">
-        <is>
-          <t>Sie haben diese Fassung freigegeben (alle Felder; 2026-10-24-runde3-katalog-steuern.xlsx, Stand 23.10.2026). Ein unterschriebenes Blatt liegt uns nicht vor (Die Ergänzung der Bestätigung (2026-10-24-ergaenzung-bestaetigung-steuern.pdf) trägt keine Unterschrift). Bitte die Freigabe dieser Fassung mit Unterschrift bestätigen.</t>
-        </is>
-      </c>
-      <c r="G7" s="3" t="inlineStr"/>
-      <c r="H7" s="3" t="inlineStr"/>
-    </row>
-    <row r="8">
-      <c r="A8" s="3" t="n">
-        <v>7</v>
-      </c>
-      <c r="B8" s="3" t="inlineStr">
-        <is>
-          <t>Unterschrift fehlt</t>
-        </is>
-      </c>
-      <c r="C8" s="3" t="inlineStr">
-        <is>
-          <t>C.27 steuern.feststellungserklaerung</t>
-        </is>
-      </c>
-      <c r="D8" s="3" t="inlineStr">
-        <is>
-          <t>v4</t>
-        </is>
-      </c>
-      <c r="E8" s="3" t="inlineStr">
-        <is>
-          <t>Erklärung zur gesonderten und einheitlichen Feststellung abgeben</t>
-        </is>
-      </c>
-      <c r="F8" s="3" t="inlineStr">
-        <is>
-          <t>Sie haben diese Fassung freigegeben (alle Felder; 2026-10-24-runde3-katalog-steuern.xlsx, Stand 23.10.2026). Ein unterschriebenes Blatt liegt uns nicht vor (Die Ergänzung der Bestätigung (2026-10-24-ergaenzung-bestaetigung-steuern.pdf) trägt keine Unterschrift). Bitte die Freigabe dieser Fassung mit Unterschrift bestätigen.</t>
-        </is>
-      </c>
-      <c r="G8" s="3" t="inlineStr"/>
-      <c r="H8" s="3" t="inlineStr"/>
-    </row>
-    <row r="9">
-      <c r="A9" s="3" t="n">
-        <v>8</v>
-      </c>
-      <c r="B9" s="3" t="inlineStr">
-        <is>
-          <t>Unterschrift fehlt</t>
-        </is>
-      </c>
-      <c r="C9" s="3" t="inlineStr">
-        <is>
-          <t>C.36 steuern.oss_erklaerung</t>
-        </is>
-      </c>
-      <c r="D9" s="3" t="inlineStr">
-        <is>
-          <t>v3</t>
-        </is>
-      </c>
-      <c r="E9" s="3" t="inlineStr">
-        <is>
-          <t>OSS-Erklärung beim Bundeszentralamt für Steuern abgeben</t>
-        </is>
-      </c>
-      <c r="F9" s="3" t="inlineStr">
-        <is>
-          <t>Sie haben diese Fassung freigegeben (alle Felder; 2026-10-23-nachpruefung-vorlagen-steuern-mail.txt, Stand 23.10.2026). Ein unterschriebenes Blatt liegt uns nicht vor (Freigabe per Mail 23.10.2026; die Ergänzung der Bestätigung (2026-10-24-ergaenzung-bestaetigung-steuern.pdf) trägt keine Unterschrift). Bitte die Freigabe dieser Fassung mit Unterschrift bestätigen.</t>
-        </is>
-      </c>
-      <c r="G9" s="3" t="inlineStr"/>
-      <c r="H9" s="3" t="inlineStr"/>
-    </row>
-    <row r="10">
-      <c r="A10" s="3" t="n">
-        <v>9</v>
-      </c>
-      <c r="B10" s="3" t="inlineStr">
-        <is>
-          <t>Vorlage</t>
-        </is>
-      </c>
-      <c r="C10" s="3" t="inlineStr">
-        <is>
-          <t>rechnung</t>
-        </is>
-      </c>
-      <c r="D10" s="3" t="inlineStr">
-        <is>
-          <t>b1bf4530cee8</t>
-        </is>
-      </c>
-      <c r="E10" s="3" t="inlineStr">
-        <is>
-          <t>Rechnung</t>
-        </is>
-      </c>
-      <c r="F10" s="3" t="inlineStr">
-        <is>
-          <t>Seit Ihrer Freigabe geändert sind nur diese Varianten: GmbH &amp; Co. KG; UG (haftungsbeschränkt) &amp; Co. KG; Storno einer Schlussrechnung mit Abschlägen (die abgesetzten Abschlagsrechnungen werden mit umgekehrtem Vorzeichen gespiegelt, E-193) – bei GmbH &amp; Co. KG / UG &amp; Co. KG die Fußzeile mit der Zeile „Persönlich haftende Gesellschafterin: …“ (Angaben der Komplementärin, E-193). Die übrigen 30 von 33 Varianten (Rechtsformen, Länder, Kleinunternehmer, Schlussrechnung, Storno) sind unverändert; für sie gilt Ihre Freigabe weiter. Beispiel-PDFs der geänderten Varianten: vorlagen/rechnung-gmbh-co-kg.pdf, vorlagen/rechnung-ug-co-kg.pdf, vorlagen/rechnung-storno-schlussrechnung.pdf. Bitte die geänderten Varianten durchsehen und bestätigen.</t>
-        </is>
-      </c>
-      <c r="G10" s="3" t="inlineStr"/>
-      <c r="H10" s="3" t="inlineStr"/>
-    </row>
-    <row r="11">
-      <c r="A11" s="3" t="n">
-        <v>10</v>
-      </c>
-      <c r="B11" s="3" t="inlineStr">
-        <is>
-          <t>Vorlage</t>
-        </is>
-      </c>
-      <c r="C11" s="3" t="inlineStr">
-        <is>
-          <t>ust_voranmeldung</t>
-        </is>
-      </c>
-      <c r="D11" s="3" t="inlineStr">
-        <is>
-          <t>c0939d610d67</t>
-        </is>
-      </c>
-      <c r="E11" s="3" t="inlineStr">
-        <is>
-          <t>Umsatzsteuer-Voranmeldung</t>
-        </is>
-      </c>
-      <c r="F11" s="3" t="inlineStr">
-        <is>
-          <t>Ein unterschriebenes Blatt liegt uns nicht vor (Die Ergänzung der Bestätigung trägt keine Unterschrift). Inhalt seit Ihrer Freigabe unverändert – bitte nur die Freigabe mit Unterschrift bestätigen.</t>
-        </is>
-      </c>
-      <c r="G11" s="3" t="inlineStr"/>
-      <c r="H11" s="3" t="inlineStr"/>
-    </row>
-    <row r="12">
-      <c r="A12" s="3" t="n">
-        <v>11</v>
-      </c>
-      <c r="B12" s="3" t="inlineStr">
-        <is>
-          <t>Vorlage</t>
-        </is>
-      </c>
-      <c r="C12" s="3" t="inlineStr">
-        <is>
-          <t>oss_meldung</t>
-        </is>
-      </c>
-      <c r="D12" s="3" t="inlineStr">
-        <is>
-          <t>4416d2cf8a9c</t>
-        </is>
-      </c>
-      <c r="E12" s="3" t="inlineStr">
-        <is>
-          <t>OSS-Erklärung (One-Stop-Shop)</t>
-        </is>
-      </c>
-      <c r="F12" s="3" t="inlineStr">
-        <is>
-          <t>Ein unterschriebenes Blatt liegt uns nicht vor (Die Ergänzung der Bestätigung trägt keine Unterschrift). Inhalt seit Ihrer Freigabe unverändert – bitte nur die Freigabe mit Unterschrift bestätigen.</t>
-        </is>
-      </c>
-      <c r="G12" s="3" t="inlineStr"/>
-      <c r="H12" s="3" t="inlineStr"/>
-    </row>
-    <row r="13">
-      <c r="A13" s="3" t="n">
-        <v>12</v>
-      </c>
-      <c r="B13" s="3" t="inlineStr">
-        <is>
-          <t>Vorlage</t>
-        </is>
-      </c>
-      <c r="C13" s="3" t="inlineStr">
-        <is>
-          <t>zm_meldung</t>
-        </is>
-      </c>
-      <c r="D13" s="3" t="inlineStr">
-        <is>
-          <t>332a518a08d5</t>
-        </is>
-      </c>
-      <c r="E13" s="3" t="inlineStr">
-        <is>
-          <t>Zusammenfassende Meldung</t>
-        </is>
-      </c>
-      <c r="F13" s="3" t="inlineStr">
-        <is>
-          <t>Ein unterschriebenes Blatt liegt uns nicht vor (Die Ergänzung der Bestätigung trägt keine Unterschrift). Inhalt seit Ihrer Freigabe unverändert – bitte nur die Freigabe mit Unterschrift bestätigen.</t>
-        </is>
-      </c>
-      <c r="G13" s="3" t="inlineStr"/>
-      <c r="H13" s="3" t="inlineStr"/>
-    </row>
-    <row r="14">
-      <c r="A14" s="3" t="n">
-        <v>13</v>
-      </c>
-      <c r="B14" s="3" t="inlineStr">
-        <is>
-          <t>Vorlage</t>
-        </is>
-      </c>
-      <c r="C14" s="3" t="inlineStr">
-        <is>
-          <t>steuererklaerung</t>
-        </is>
-      </c>
-      <c r="D14" s="3" t="inlineStr">
-        <is>
-          <t>c5f459479a06</t>
-        </is>
-      </c>
-      <c r="E14" s="3" t="inlineStr">
-        <is>
-          <t>Unterlagen zur Steuererklärung</t>
-        </is>
-      </c>
-      <c r="F14" s="3" t="inlineStr">
-        <is>
-          <t>Ein unterschriebenes Blatt liegt uns nicht vor (Die Ergänzung der Bestätigung trägt keine Unterschrift). Inhalt seit Ihrer Freigabe unverändert – bitte nur die Freigabe mit Unterschrift bestätigen.</t>
-        </is>
-      </c>
-      <c r="G14" s="3" t="inlineStr"/>
-      <c r="H14" s="3" t="inlineStr"/>
-    </row>
-    <row r="15">
-      <c r="A15" s="3" t="n">
-        <v>14</v>
-      </c>
-      <c r="B15" s="3" t="inlineStr">
-        <is>
-          <t>Vorlage</t>
-        </is>
-      </c>
-      <c r="C15" s="3" t="inlineStr">
-        <is>
-          <t>kassenbuch</t>
-        </is>
-      </c>
-      <c r="D15" s="3" t="inlineStr">
-        <is>
-          <t>9cad79a55cbc</t>
-        </is>
-      </c>
-      <c r="E15" s="3" t="inlineStr">
-        <is>
-          <t>Kassenbuch</t>
-        </is>
-      </c>
-      <c r="F15" s="3" t="inlineStr">
-        <is>
-          <t>Ein unterschriebenes Blatt liegt uns nicht vor (Die Ergänzung der Bestätigung trägt keine Unterschrift). Inhalt seit Ihrer Freigabe unverändert – bitte nur die Freigabe mit Unterschrift bestätigen.</t>
-        </is>
-      </c>
-      <c r="G15" s="3" t="inlineStr"/>
-      <c r="H15" s="3" t="inlineStr"/>
-    </row>
-    <row r="16">
-      <c r="A16" s="3" t="n">
-        <v>15</v>
-      </c>
-      <c r="B16" s="3" t="inlineStr">
-        <is>
-          <t>Vorlage</t>
-        </is>
-      </c>
-      <c r="C16" s="3" t="inlineStr">
-        <is>
-          <t>aufbewahrung</t>
-        </is>
-      </c>
-      <c r="D16" s="3" t="inlineStr">
-        <is>
-          <t>0ebd0adde12a</t>
-        </is>
-      </c>
-      <c r="E16" s="3" t="inlineStr">
-        <is>
-          <t>Aufbewahrungsplan</t>
-        </is>
-      </c>
-      <c r="F16" s="3" t="inlineStr">
-        <is>
-          <t>Ein unterschriebenes Blatt liegt uns nicht vor (Die Ergänzung der Bestätigung trägt keine Unterschrift). Inhalt seit Ihrer Freigabe unverändert – bitte nur die Freigabe mit Unterschrift bestätigen.</t>
-        </is>
-      </c>
-      <c r="G16" s="3" t="inlineStr"/>
-      <c r="H16" s="3" t="inlineStr"/>
-    </row>
-    <row r="17">
-      <c r="A17" s="3" t="n">
-        <v>16</v>
-      </c>
-      <c r="B17" s="3" t="inlineStr">
-        <is>
-          <t>Vorlage</t>
-        </is>
-      </c>
-      <c r="C17" s="3" t="inlineStr">
-        <is>
-          <t>sv_meldedaten</t>
-        </is>
-      </c>
-      <c r="D17" s="3" t="inlineStr">
-        <is>
-          <t>6823730ddb14</t>
-        </is>
-      </c>
-      <c r="E17" s="3" t="inlineStr">
-        <is>
-          <t>Personalfragebogen (Daten für die Anmeldung)</t>
-        </is>
-      </c>
-      <c r="F17" s="3" t="inlineStr">
-        <is>
-          <t>Ein unterschriebenes Blatt liegt uns nicht vor (Die Ergänzung der Bestätigung trägt keine Unterschrift). Inhalt seit Ihrer Freigabe unverändert – bitte nur die Freigabe mit Unterschrift bestätigen.</t>
-        </is>
-      </c>
-      <c r="G17" s="3" t="inlineStr"/>
-      <c r="H17" s="3" t="inlineStr"/>
-    </row>
-    <row r="18">
-      <c r="A18" s="3" t="n">
-        <v>17</v>
-      </c>
-      <c r="B18" s="3" t="inlineStr">
-        <is>
-          <t>Vorlage</t>
-        </is>
-      </c>
-      <c r="C18" s="3" t="inlineStr">
-        <is>
-          <t>bilanz_guv</t>
-        </is>
-      </c>
-      <c r="D18" s="3" t="inlineStr">
-        <is>
-          <t>a266993aadfd</t>
-        </is>
-      </c>
-      <c r="E18" s="3" t="inlineStr">
-        <is>
-          <t>Bilanz und Gewinn- und Verlustrechnung</t>
-        </is>
-      </c>
-      <c r="F18" s="3" t="inlineStr">
-        <is>
-          <t>Seit Ihrer Freigabe geändert sind nur diese Varianten: Hilfetext eines Formularfelds: „Steuerberater“ statt Ihres Namens (das gedruckte Dokument ist unverändert). Die übrigen 29 von 30 Varianten (Rechtsformen, Länder, Kleinunternehmer) sind unverändert; für sie gilt Ihre Freigabe weiter. Ein unterschriebenes Blatt liegt uns nicht vor (Die Mail vom 25.10.2026 nennt den Nachtrag „unterschrieben“; die angehängte Datei (und 2026-10-25-nachtrag-bilanz-steuern.pdf) trägt keine Unterschrift). Bitte die geänderten Varianten durchsehen und bestätigen.</t>
-        </is>
-      </c>
-      <c r="G18" s="3" t="inlineStr"/>
-      <c r="H18" s="3" t="inlineStr"/>
-    </row>
-    <row r="19">
-      <c r="A19" s="3" t="n">
-        <v>18</v>
-      </c>
-      <c r="B19" s="3" t="inlineStr">
-        <is>
-          <t>Nennung im Vermerk</t>
-        </is>
-      </c>
-      <c r="C19" s="3" t="inlineStr">
-        <is>
-          <t>alle</t>
-        </is>
-      </c>
-      <c r="D19" s="3" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
-      </c>
-      <c r="E19" s="3" t="inlineStr">
-        <is>
-          <t>Rolle statt Name</t>
-        </is>
-      </c>
-      <c r="F19" s="3" t="inlineStr">
-        <is>
-          <t>Die App nennt Personen nicht mehr. Bisher mit Ihrem Namen und der Kanzlei (Ihre Bestätigung vom 23.10.2026); künftig nennt der Vermerk Ihre Rolle: „Fachlich durchgesehen von einem Steuerberater (Stand …) – ohne Gewähr für den Einzelfall.“ (bei Einschränkungen mit dem Zusatz in Klammern, bei offenen Punkten „teilweise“). Bitte bestätigen, dass die Nennung der Rolle so in Ordnung ist.</t>
-        </is>
-      </c>
-      <c r="G19" s="3" t="inlineStr"/>
-      <c r="H19" s="3" t="inlineStr"/>
-    </row>
   </sheetData>
   <dataValidations count="1">
-    <dataValidation sqref="G2:G19" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="G2:G6" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"bestätigt,ändern (Anmerkung),nicht mein Bereich"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" fitToHeight="0" fitToWidth="1"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:B13"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="30" customWidth="1" min="1" max="1"/>
-    <col width="90" customWidth="1" min="2" max="2"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Bestätigung der Nachprüfung – Steuerberater</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr"/>
-    </row>
-    <row r="3" ht="90" customHeight="1">
-      <c r="A3" s="4" t="inlineStr">
-        <is>
-          <t>Ich habe die Positionen der Nachprüfliste vom 25.10.2026, die ich in der Spalte „Entscheidung“ mit „bestätigt“ markiert habe, in der jeweils genannten Fassung (Version bzw. Prüfsumme) fachlich geprüft bzw. durchgesehen. Sie sind nach meiner Prüfung zum genannten Stand zutreffend. Positionen mit „ändern“ oder „nicht mein Bereich“ sind nicht umfasst; für sie darf kein Vermerk angezeigt werden. Ändert sich ein Eintrag (neue Version) oder eine Vorlage (andere Prüfsumme), gilt diese Bestätigung dafür nicht mehr. Die Prüfung betrifft die allgemeinen Inhalte, nicht ihre Anwendung im Einzelfall.</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr"/>
-    </row>
-    <row r="5" ht="45" customHeight="1">
-      <c r="A5" s="4" t="inlineStr">
-        <is>
-          <t>Anzeige in der App (nur bei bestätigten Positionen, ohne Namen, mit der Rolle): „Fachlich durchgesehen von einem Steuerberater (Stand …) – ohne Gewähr für den Einzelfall.“</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr"/>
-    </row>
-    <row r="7">
-      <c r="A7" s="5" t="inlineStr">
-        <is>
-          <t>Stand der Prüfung:</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr"/>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr"/>
-    </row>
-    <row r="9">
-      <c r="A9" s="5" t="inlineStr">
-        <is>
-          <t>Ort, Datum:</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr"/>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr"/>
-    </row>
-    <row r="11">
-      <c r="A11" s="5" t="inlineStr">
-        <is>
-          <t>Unterschrift:</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr"/>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr"/>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>(Steuerberater)</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="2">
-    <mergeCell ref="A3:B3"/>
-    <mergeCell ref="A5:B5"/>
-  </mergeCells>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
 </file>
--- a/docs/freigabe-katalog/versand-2026-10-25-nachpruefung/steuern/Betriebsklar-Nachpruefliste-Steuerberater.xlsx
+++ b/docs/freigabe-katalog/versand-2026-10-25-nachpruefung/steuern/Betriebsklar-Nachpruefliste-Steuerberater.xlsx
@@ -527,7 +527,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:H6"/>
+  <dimension ref="A1:H5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -684,67 +684,35 @@
       </c>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>Vorlage</t>
+          <t>Nennung im Vermerk</t>
         </is>
       </c>
       <c r="C5" s="3" t="inlineStr">
         <is>
-          <t>bilanz_guv</t>
+          <t>alle</t>
         </is>
       </c>
       <c r="D5" s="3" t="inlineStr">
         <is>
-          <t>a266993aadfd</t>
+          <t>–</t>
         </is>
       </c>
       <c r="E5" s="3" t="inlineStr">
         <is>
-          <t>Bilanz und Gewinn- und Verlustrechnung</t>
+          <t>Rolle statt Name</t>
         </is>
       </c>
       <c r="F5" s="3" t="inlineStr">
         <is>
-          <t>Seit Ihrer Freigabe geändert sind nur diese Varianten: Hilfetext eines Formularfelds: „Steuerberater“ statt Ihres Namens (das gedruckte Dokument ist unverändert). Die übrigen 29 von 30 Varianten (Rechtsformen, Länder, Kleinunternehmer) sind unverändert; für sie gilt Ihre Freigabe weiter, die App zeigt dort den Vermerk. Bitte sehen Sie die geänderten Varianten durch und bestätigen Sie sie per E-Mail.</t>
+          <t>Die App nennt Personen nicht mehr. Bisher mit Ihrem Namen und der Kanzlei (Ihre Bestätigung vom 23.10.2026); künftig nennt der Vermerk Ihre Rolle: „Fachlich durchgesehen von einem Steuerberater (Stand …) – ohne Gewähr für den Einzelfall.“ (bei Einschränkungen mit dem Zusatz in Klammern, bei offenen Punkten „teilweise“). Bitte bestätigen Sie per E-Mail, dass die Nennung der Rolle so in Ordnung ist.</t>
         </is>
       </c>
       <c r="G5" s="3" t="inlineStr"/>
       <c r="H5" s="3" t="inlineStr"/>
     </row>
-    <row r="6">
-      <c r="A6" s="3" t="n">
-        <v>5</v>
-      </c>
-      <c r="B6" s="3" t="inlineStr">
-        <is>
-          <t>Nennung im Vermerk</t>
-        </is>
-      </c>
-      <c r="C6" s="3" t="inlineStr">
-        <is>
-          <t>alle</t>
-        </is>
-      </c>
-      <c r="D6" s="3" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
-      </c>
-      <c r="E6" s="3" t="inlineStr">
-        <is>
-          <t>Rolle statt Name</t>
-        </is>
-      </c>
-      <c r="F6" s="3" t="inlineStr">
-        <is>
-          <t>Die App nennt Personen nicht mehr. Bisher mit Ihrem Namen und der Kanzlei (Ihre Bestätigung vom 23.10.2026); künftig nennt der Vermerk Ihre Rolle: „Fachlich durchgesehen von einem Steuerberater (Stand …) – ohne Gewähr für den Einzelfall.“ (bei Einschränkungen mit dem Zusatz in Klammern, bei offenen Punkten „teilweise“). Bitte bestätigen Sie per E-Mail, dass die Nennung der Rolle so in Ordnung ist.</t>
-        </is>
-      </c>
-      <c r="G6" s="3" t="inlineStr"/>
-      <c r="H6" s="3" t="inlineStr"/>
-    </row>
   </sheetData>
   <dataValidations count="1">
-    <dataValidation sqref="G2:G6" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="G2:G5" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"bestätigt,ändern (Anmerkung),nicht mein Bereich"</formula1>
     </dataValidation>
   </dataValidations>
